--- a/Training.xlsx
+++ b/Training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95863482-5A2E-4A4B-B4B1-755EA43C4B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B65A8E-C88D-47D2-BAF6-E83680611687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A10298D-1098-4C5D-B2FC-6CE2C7B960BA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="88">
   <si>
     <t>Contest Title</t>
   </si>
@@ -190,6 +190,114 @@
   </si>
   <si>
     <t>Tuning</t>
+  </si>
+  <si>
+    <t>abc478</t>
+  </si>
+  <si>
+    <t>abc477</t>
+  </si>
+  <si>
+    <t>abc476</t>
+  </si>
+  <si>
+    <t>abc475</t>
+  </si>
+  <si>
+    <t>AtCoder Beginner Contest 478</t>
+  </si>
+  <si>
+    <t>AtCoder Beginner Contest 477</t>
+  </si>
+  <si>
+    <t>AtCoder Beginner Contest 476</t>
+  </si>
+  <si>
+    <t>AtCoder Beginner Contest 475</t>
+  </si>
+  <si>
+    <t>mnclr</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Walk the Line</t>
+  </si>
+  <si>
+    <t>Alphametic Prime</t>
+  </si>
+  <si>
+    <t>Quiz Competition: Qualifiers</t>
+  </si>
+  <si>
+    <t>Rectangle Filling</t>
+  </si>
+  <si>
+    <t>Has Many Divisors</t>
+  </si>
+  <si>
+    <t>Appender</t>
+  </si>
+  <si>
+    <t>Wild Card</t>
+  </si>
+  <si>
+    <t>Third Largest Number</t>
+  </si>
+  <si>
+    <t>Automat</t>
+  </si>
+  <si>
+    <t>Min-Max Swap</t>
+  </si>
+  <si>
+    <t>Chebyshev Cafe</t>
+  </si>
+  <si>
+    <t>Increasing Popcount</t>
+  </si>
+  <si>
+    <t>Traffic Light</t>
+  </si>
+  <si>
+    <t>Standing Outliers</t>
+  </si>
+  <si>
+    <t>Range Search Query</t>
+  </si>
+  <si>
+    <t>Masking Tape</t>
+  </si>
+  <si>
+    <t>Wheel Distance</t>
+  </si>
+  <si>
+    <t>Count Cells in a Window</t>
+  </si>
+  <si>
+    <t>Frequency Query on Tree</t>
+  </si>
+  <si>
+    <t>Grapes</t>
+  </si>
+  <si>
+    <t>Topping</t>
+  </si>
+  <si>
+    <t>Sort Subarray</t>
+  </si>
+  <si>
+    <t>Range Set Insertion Query</t>
+  </si>
+  <si>
+    <t>lt and le</t>
+  </si>
+  <si>
+    <t>Min-First Search</t>
+  </si>
+  <si>
+    <t>Division Point Hull</t>
   </si>
 </sst>
 </file>
@@ -282,7 +390,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -336,6 +444,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -655,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01753D5-134D-4CF1-9279-870645A5C417}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -952,8 +1069,8 @@
       <c r="F16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>42</v>
+      <c r="G16" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -997,7 +1114,7 @@
       <c r="B19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="16" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1005,6 +1122,9 @@
       </c>
       <c r="E19" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="F19" s="3">
+        <v>100</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>8</v>
@@ -1013,12 +1133,15 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="F20" s="1">
+        <v>200</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>8</v>
@@ -1027,12 +1150,15 @@
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>47</v>
+      </c>
+      <c r="F21" s="1">
+        <v>300</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>8</v>
@@ -1041,12 +1167,15 @@
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="C22" s="21"/>
       <c r="D22" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>48</v>
+      </c>
+      <c r="F22" s="1">
+        <v>400</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>8</v>
@@ -1055,12 +1184,15 @@
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>49</v>
+      </c>
+      <c r="F23" s="1">
+        <v>450</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>8</v>
@@ -1069,12 +1201,15 @@
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="F24" s="1">
+        <v>500</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>8</v>
@@ -1083,16 +1218,534 @@
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="F25" s="2">
+        <v>600</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="3">
+        <v>100</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="19">
+        <v>200</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="19">
+        <v>300</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="19">
+        <v>400</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" s="19">
+        <v>475</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="19">
+        <v>525</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="2">
+        <v>625</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" s="19">
+        <v>100</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="19">
+        <v>200</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="19">
+        <v>300</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="19">
+        <v>400</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="19">
+        <v>450</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" s="19">
+        <v>525</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F39" s="2">
+        <v>625</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="19">
+        <v>100</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="19">
+        <v>200</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" s="19">
+        <v>300</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" s="19">
+        <v>425</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="19">
+        <v>450</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="19">
+        <v>525</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F46" s="2">
+        <v>625</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F47" s="19">
+        <v>100</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="19">
+        <v>200</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="19">
+        <v>300</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="19">
+        <v>400</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="19">
+        <v>475</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F52" s="19">
+        <v>525</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" s="2">
+        <v>575</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="21">
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="C40:C46"/>
+    <mergeCell ref="A47:A53"/>
+    <mergeCell ref="B47:B53"/>
+    <mergeCell ref="C47:C53"/>
+    <mergeCell ref="A26:A32"/>
+    <mergeCell ref="B26:B32"/>
+    <mergeCell ref="C26:C32"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="B33:B39"/>
+    <mergeCell ref="C33:C39"/>
     <mergeCell ref="A19:A25"/>
     <mergeCell ref="B19:B25"/>
     <mergeCell ref="C19:C25"/>
